--- a/1. 기획문서/0. Data/버튜버_데뷔일정_2026-07_08.xlsx
+++ b/1. 기획문서/0. Data/버튜버_데뷔일정_2026-07_08.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 일정" sheetId="1" r:id="R73437bcaef8d4c22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07 캘린더" sheetId="2" r:id="Raa975d1c511e427b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08 캘린더" sheetId="3" r:id="R3fd3c47986c74023"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입력 기준" sheetId="4" r:id="R0de0fb14013d4c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체 일정" sheetId="1" r:id="R2a98735a66634ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07 캘린더" sheetId="2" r:id="R3d6cde7ffbb4420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08 캘린더" sheetId="3" r:id="R809832d4c36746e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입력 기준" sheetId="4" r:id="Rd8610be881c5468c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -51,7 +51,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="hh:mm"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -130,8 +130,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="맑은 고딕"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -193,8 +199,23 @@
         <x:fgColor rgb="FF7C3AED"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F2B3E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFB7E0F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="17">
+  <x:borders count="19">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -348,11 +369,21 @@
         <x:color rgb="FFD9E2EC"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="123">
+  <x:cellXfs count="137">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -632,18 +663,58 @@
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="5">
+  <x:dxfs count="8">
     <x:dxf>
       <x:font>
         <x:b/>
         <x:color rgb="FF087D2B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9FBEF"/>
         </x:patternFill>
       </x:fill>
@@ -654,7 +725,7 @@
         <x:color rgb="FF0B5BC4"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF3FF"/>
         </x:patternFill>
       </x:fill>
@@ -665,7 +736,7 @@
         <x:color rgb="FF7C3AED"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF2ECFF"/>
         </x:patternFill>
       </x:fill>
@@ -676,7 +747,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDECEC"/>
         </x:patternFill>
       </x:fill>
@@ -687,8 +758,41 @@
         <x:color rgb="FFA15C00"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF7E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF215E21"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF7E6"/>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -938,9 +1042,11 @@
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="31" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="50" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="48" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="48" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="17" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -980,10 +1086,12 @@
       <x:c r="L1" s="5" t="str">
         <x:v>버튜버 데뷔 일정 | 2026년 7월~8월</x:v>
       </x:c>
+      <x:c r="M1" s="126"/>
+      <x:c r="N1" s="126"/>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>치지직·SOOP 공개 일정을 기준으로 작성한 1차 확인본입니다. 시간은 한국시간(KST)이며 방송 전 원문 재확인을 권장합니다.</x:v>
+        <x:v>공식 방송 채널 URL과 일정 근거 URL을 분리한 수정본입니다. 채널 ID가 끝까지 확인되지 않은 항목은 임의 링크 없이 ‘미확인’으로 표시했습니다.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -1070,7 +1178,7 @@
       <x:c r="I5" s="1"/>
       <x:c r="J5" s="61" t="n">
         <x:f>COUNTIF($L$9:$L$200,"검토 필요")</x:f>
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K5" s="62"/>
       <x:c r="L5" s="63"/>
@@ -1132,13 +1240,19 @@
         <x:v>소속·비고</x:v>
       </x:c>
       <x:c r="J8" s="74" t="str">
-        <x:v>출처 URL</x:v>
+        <x:v>방송 채널 URL</x:v>
       </x:c>
       <x:c r="K8" s="74" t="str">
         <x:v>시간 확인</x:v>
       </x:c>
       <x:c r="L8" s="75" t="str">
         <x:v>등록 검토</x:v>
+      </x:c>
+      <x:c r="M8" s="133" t="str">
+        <x:v>일정 근거 URL</x:v>
+      </x:c>
+      <x:c r="N8" s="132" t="str">
+        <x:v>채널 검증</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -1170,7 +1284,7 @@
         <x:v>웰컴버추얼</x:v>
       </x:c>
       <x:c r="J9" s="83" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/a0714/post/166790429</x:v>
+        <x:v>https://www.sooplive.com/station/aarong37</x:v>
       </x:c>
       <x:c r="K9" s="86" t="str">
         <x:v>미공지</x:v>
@@ -1179,6 +1293,12 @@
         <x:f>IF(OR(K9="미공지",K9="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>검토 필요</x:v>
       </x:c>
+      <x:c r="M9" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/aarong37/post/199365231</x:v>
+      </x:c>
+      <x:c r="N9" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="87" t="n">
@@ -1211,7 +1331,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J10" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/bps1017/post/166829897</x:v>
+        <x:v>https://www.sooplive.com/station/hetty0v0</x:v>
       </x:c>
       <x:c r="K10" s="87" t="str">
         <x:v>확인</x:v>
@@ -1220,6 +1340,12 @@
         <x:f>IF(OR(K10="미공지",K10="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M10" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/hetty0v0/post/198977419</x:v>
+      </x:c>
+      <x:c r="N10" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
       <x:c r="A11" s="87" t="n">
@@ -1252,7 +1378,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J11" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/mate4077</x:v>
+        <x:v>https://www.sooplive.com/station/matae6</x:v>
       </x:c>
       <x:c r="K11" s="87" t="str">
         <x:v>확인</x:v>
@@ -1261,6 +1387,12 @@
         <x:f>IF(OR(K11="미공지",K11="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M11" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/matae6</x:v>
+      </x:c>
+      <x:c r="N11" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="34" customHeight="1">
       <x:c r="A12" s="87" t="n">
@@ -1293,7 +1425,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J12" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/harobangil/post/166904326</x:v>
+        <x:v>https://www.sooplive.com/station/2dohae</x:v>
       </x:c>
       <x:c r="K12" s="87" t="str">
         <x:v>확인</x:v>
@@ -1302,6 +1434,12 @@
         <x:f>IF(OR(K12="미공지",K12="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M12" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/2dohae/board/124245601</x:v>
+      </x:c>
+      <x:c r="N12" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
       <x:c r="A13" s="87" t="n">
@@ -1332,7 +1470,7 @@
       </x:c>
       <x:c r="I13" s="84" t="str"/>
       <x:c r="J13" s="84" t="str">
-        <x:v>https://x.com/orbitaofbehind</x:v>
+        <x:v>https://chzzk.naver.com/80c2494ca15ba21b8a4ae8d955807e2b</x:v>
       </x:c>
       <x:c r="K13" s="87" t="str">
         <x:v>확인</x:v>
@@ -1341,6 +1479,12 @@
         <x:f>IF(OR(K13="미공지",K13="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M13" s="134" t="str">
+        <x:v>https://x.com/orbitaofbehind</x:v>
+      </x:c>
+      <x:c r="N13" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
       <x:c r="A14" s="87" t="n">
@@ -1361,17 +1505,17 @@
         <x:v>드라</x:v>
       </x:c>
       <x:c r="G14" s="87" t="str">
-        <x:v>최초 데뷔</x:v>
+        <x:v>플랫폼 이적</x:v>
       </x:c>
       <x:c r="H14" s="87" t="str">
         <x:f>IF(B14&lt;$B$3,"완료",IF(B14=$B$3,"당일","예정"))</x:f>
         <x:v>완료</x:v>
       </x:c>
       <x:c r="I14" s="84" t="str">
-        <x:v>웰컴버추얼</x:v>
+        <x:v>SOOP 이적 첫 방송·최초 데뷔 집계 제외 권장</x:v>
       </x:c>
       <x:c r="J14" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/dragonrabbit/post/166992056</x:v>
+        <x:v>https://www.sooplive.com/station/bjdra0845</x:v>
       </x:c>
       <x:c r="K14" s="87" t="str">
         <x:v>미공지</x:v>
@@ -1380,6 +1524,12 @@
         <x:f>IF(OR(K14="미공지",K14="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>검토 필요</x:v>
       </x:c>
+      <x:c r="M14" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/bjdra0845/post/200201497</x:v>
+      </x:c>
+      <x:c r="N14" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
       <x:c r="A15" s="87" t="n">
@@ -1402,22 +1552,29 @@
         <x:v>토척새</x:v>
       </x:c>
       <x:c r="G15" s="87" t="str">
-        <x:v>최초 데뷔</x:v>
+        <x:v>재데뷔 여부 확인</x:v>
       </x:c>
       <x:c r="H15" s="87" t="str">
         <x:f>IF(B15&lt;$B$3,"완료",IF(B15=$B$3,"당일","예정"))</x:f>
         <x:v>완료</x:v>
       </x:c>
-      <x:c r="I15" s="84" t="str"/>
+      <x:c r="I15" s="84" t="str">
+        <x:v>기존 채널 방송 이력 확인됨·최초 데뷔 분류 재검토</x:v>
+      </x:c>
       <x:c r="J15" s="84" t="str">
+        <x:v>https://chzzk.naver.com/5f04c53cd57e998583424fdd5af05ed9</x:v>
+      </x:c>
+      <x:c r="K15" s="87" t="str">
+        <x:v>확인</x:v>
+      </x:c>
+      <x:c r="L15" s="87" t="str">
+        <x:v>검토 필요</x:v>
+      </x:c>
+      <x:c r="M15" s="134" t="str">
         <x:v>https://x.com/TPRPWHDAKF/status/2068694382371537052</x:v>
       </x:c>
-      <x:c r="K15" s="87" t="str">
-        <x:v>확인</x:v>
-      </x:c>
-      <x:c r="L15" s="87" t="str">
-        <x:f>IF(OR(K15="미공지",K15="재확인 필요"),"검토 필요","등록 가능")</x:f>
-        <x:v>등록 가능</x:v>
+      <x:c r="N15" s="125" t="str">
+        <x:v>확인</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1451,7 +1608,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J16" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/soren9900/post/167082005</x:v>
+        <x:v>https://www.sooplive.com/station/whitesaerin</x:v>
       </x:c>
       <x:c r="K16" s="87" t="str">
         <x:v>확인</x:v>
@@ -1460,6 +1617,12 @@
         <x:f>IF(OR(K16="미공지",K16="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M16" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/whitesaerin/post/200210185</x:v>
+      </x:c>
+      <x:c r="N16" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
       <x:c r="A17" s="87" t="n">
@@ -1492,7 +1655,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J17" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/soramsoram/post/167115947</x:v>
+        <x:v>https://www.sooplive.com/station/soram0324</x:v>
       </x:c>
       <x:c r="K17" s="87" t="str">
         <x:v>확인</x:v>
@@ -1501,6 +1664,12 @@
         <x:f>IF(OR(K17="미공지",K17="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M17" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/soram0324/post/200342713</x:v>
+      </x:c>
+      <x:c r="N17" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
       <x:c r="A18" s="87" t="n">
@@ -1531,7 +1700,7 @@
       </x:c>
       <x:c r="I18" s="84" t="str"/>
       <x:c r="J18" s="84" t="str">
-        <x:v>https://x.com/shuyo_chzzk/status/2071867582341104076</x:v>
+        <x:v>https://chzzk.naver.com/8c615cb598cc8dbce78ac4c938a569b6</x:v>
       </x:c>
       <x:c r="K18" s="87" t="str">
         <x:v>확인</x:v>
@@ -1540,6 +1709,12 @@
         <x:f>IF(OR(K18="미공지",K18="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M18" s="135" t="str">
+        <x:v>https://x.com/shuyo_chzzk/status/2071867582341104076</x:v>
+      </x:c>
+      <x:c r="N18" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
       <x:c r="A19" s="87" t="n">
@@ -1572,7 +1747,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J19" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/haekong2/post/167250331</x:v>
+        <x:v>https://www.sooplive.com/station/yami875</x:v>
       </x:c>
       <x:c r="K19" s="87" t="str">
         <x:v>확인</x:v>
@@ -1581,6 +1756,12 @@
         <x:f>IF(OR(K19="미공지",K19="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M19" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/yami875/post/200694643</x:v>
+      </x:c>
+      <x:c r="N19" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
       <x:c r="A20" s="87" t="n">
@@ -1611,7 +1792,7 @@
       </x:c>
       <x:c r="I20" s="84" t="str"/>
       <x:c r="J20" s="84" t="str">
-        <x:v>https://chzzk.naver.com/video/14105462</x:v>
+        <x:v>https://chzzk.naver.com/2486f2222390ebc4d6dd67edd8b6076d</x:v>
       </x:c>
       <x:c r="K20" s="87" t="str">
         <x:v>확인</x:v>
@@ -1620,6 +1801,12 @@
         <x:f>IF(OR(K20="미공지",K20="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M20" s="135" t="str">
+        <x:v>https://chzzk.naver.com/video/14105462</x:v>
+      </x:c>
+      <x:c r="N20" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="34" customHeight="1">
       <x:c r="A21" s="87" t="n">
@@ -1652,7 +1839,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J21" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/jamstar/post/167385933</x:v>
+        <x:v>https://www.sooplive.com/station/twinkle0811</x:v>
       </x:c>
       <x:c r="K21" s="87" t="str">
         <x:v>확인</x:v>
@@ -1661,6 +1848,12 @@
         <x:f>IF(OR(K21="미공지",K21="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M21" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/twinkle0811/post/200932003</x:v>
+      </x:c>
+      <x:c r="N21" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="34" customHeight="1">
       <x:c r="A22" s="87" t="n">
@@ -1693,7 +1886,7 @@
         <x:v>오르비웨이 아스테아</x:v>
       </x:c>
       <x:c r="J22" s="84" t="str">
-        <x:v>https://x.com/orbiway_ent/status/2071098629188948360</x:v>
+        <x:v>https://chzzk.naver.com/3bc90b22f6b7925e5b92767562f44f3b</x:v>
       </x:c>
       <x:c r="K22" s="87" t="str">
         <x:v>확인</x:v>
@@ -1702,6 +1895,12 @@
         <x:f>IF(OR(K22="미공지",K22="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M22" s="135" t="str">
+        <x:v>https://x.com/orbiway_ent/status/2071098629188948360</x:v>
+      </x:c>
+      <x:c r="N22" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
       <x:c r="A23" s="87" t="n">
@@ -1734,7 +1933,7 @@
         <x:v>오르비웨이 아스테아</x:v>
       </x:c>
       <x:c r="J23" s="84" t="str">
-        <x:v>https://x.com/orbiway_ent/status/2071098629188948360</x:v>
+        <x:v>https://chzzk.naver.com/cfb55fb02bdcbf17c3eb0bd756ee7762</x:v>
       </x:c>
       <x:c r="K23" s="87" t="str">
         <x:v>확인</x:v>
@@ -1743,6 +1942,12 @@
         <x:f>IF(OR(K23="미공지",K23="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M23" s="134" t="str">
+        <x:v>https://x.com/orbiway_ent/status/2071098629188948360</x:v>
+      </x:c>
+      <x:c r="N23" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
       <x:c r="A24" s="87" t="n">
@@ -1775,7 +1980,7 @@
         <x:v>오르비웨이 아스테아</x:v>
       </x:c>
       <x:c r="J24" s="84" t="str">
-        <x:v>https://x.com/orbiway_ent/status/2071098629188948360</x:v>
+        <x:v>https://chzzk.naver.com/dd34d48439b7feee08b53cb4063cb0fd</x:v>
       </x:c>
       <x:c r="K24" s="87" t="str">
         <x:v>확인</x:v>
@@ -1784,6 +1989,12 @@
         <x:f>IF(OR(K24="미공지",K24="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M24" s="135" t="str">
+        <x:v>https://x.com/orbiway_ent/status/2071098629188948360</x:v>
+      </x:c>
+      <x:c r="N24" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="34" customHeight="1">
       <x:c r="A25" s="87" t="n">
@@ -1812,7 +2023,7 @@
       </x:c>
       <x:c r="I25" s="84" t="str"/>
       <x:c r="J25" s="84" t="str">
-        <x:v>https://chzzk.naver.com/4f3e9a13356fbff9fb3a82987c85971c/videos</x:v>
+        <x:v>https://chzzk.naver.com/4f3e9a13356fbff9fb3a82987c85971c</x:v>
       </x:c>
       <x:c r="K25" s="87" t="str">
         <x:v>미공지</x:v>
@@ -1821,6 +2032,12 @@
         <x:f>IF(OR(K25="미공지",K25="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>검토 필요</x:v>
       </x:c>
+      <x:c r="M25" s="134" t="str">
+        <x:v>https://chzzk.naver.com/4f3e9a13356fbff9fb3a82987c85971c/videos</x:v>
+      </x:c>
+      <x:c r="N25" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
       <x:c r="A26" s="87" t="n">
@@ -1851,7 +2068,7 @@
       </x:c>
       <x:c r="I26" s="84" t="str"/>
       <x:c r="J26" s="84" t="str">
-        <x:v>https://www.youtube.com/shorts/3dGP68wFglc</x:v>
+        <x:v>https://chzzk.naver.com/fc2a5737e44f64a8b0ea259d8b9d1103</x:v>
       </x:c>
       <x:c r="K26" s="87" t="str">
         <x:v>확인</x:v>
@@ -1860,6 +2077,12 @@
         <x:f>IF(OR(K26="미공지",K26="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M26" s="135" t="str">
+        <x:v>https://www.youtube.com/shorts/3dGP68wFglc</x:v>
+      </x:c>
+      <x:c r="N26" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
       <x:c r="A27" s="87" t="n">
@@ -1892,7 +2115,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J27" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/haez_0526/post/167603903</x:v>
+        <x:v>https://www.sooplive.com/station/hinyacgho</x:v>
       </x:c>
       <x:c r="K27" s="87" t="str">
         <x:v>확인</x:v>
@@ -1901,6 +2124,12 @@
         <x:f>IF(OR(K27="미공지",K27="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M27" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/hinyacgho/post/201256821</x:v>
+      </x:c>
+      <x:c r="N27" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="34" customHeight="1">
       <x:c r="A28" s="87" t="n">
@@ -1933,7 +2162,7 @@
         <x:v>시간 변경 반영</x:v>
       </x:c>
       <x:c r="J28" s="84" t="str">
-        <x:v>https://x.com/TWILLIT_studio_/with_replies</x:v>
+        <x:v>https://chzzk.naver.com/1bacd9d540012f7cf0c77fa968b47394</x:v>
       </x:c>
       <x:c r="K28" s="87" t="str">
         <x:v>확인</x:v>
@@ -1942,6 +2171,12 @@
         <x:f>IF(OR(K28="미공지",K28="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M28" s="135" t="str">
+        <x:v>https://x.com/TWILLIT_studio_/with_replies</x:v>
+      </x:c>
+      <x:c r="N28" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="34" customHeight="1">
       <x:c r="A29" s="87" t="n">
@@ -1972,7 +2207,7 @@
       </x:c>
       <x:c r="I29" s="84" t="str"/>
       <x:c r="J29" s="84" t="str">
-        <x:v>https://chzzk.naver.com/2ff1e69c13a04c76a3533387d2126c61/videos</x:v>
+        <x:v>https://chzzk.naver.com/2ff1e69c13a04c76a3533387d2126c61</x:v>
       </x:c>
       <x:c r="K29" s="87" t="str">
         <x:v>확인</x:v>
@@ -1981,6 +2216,12 @@
         <x:f>IF(OR(K29="미공지",K29="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M29" s="134" t="str">
+        <x:v>https://chzzk.naver.com/2ff1e69c13a04c76a3533387d2126c61/videos</x:v>
+      </x:c>
+      <x:c r="N29" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="34" customHeight="1">
       <x:c r="A30" s="87" t="n">
@@ -2011,7 +2252,7 @@
         <x:v>Live2D 첫 공개</x:v>
       </x:c>
       <x:c r="J30" s="84" t="str">
-        <x:v>https://x.com/Rhywul</x:v>
+        <x:v>https://chzzk.id/rhywul</x:v>
       </x:c>
       <x:c r="K30" s="87" t="str">
         <x:v>미공지</x:v>
@@ -2020,6 +2261,12 @@
         <x:f>IF(OR(K30="미공지",K30="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>검토 필요</x:v>
       </x:c>
+      <x:c r="M30" s="135" t="str">
+        <x:v>https://x.com/Rhywul/status/2070595728674816067</x:v>
+      </x:c>
+      <x:c r="N30" s="125" t="str">
+        <x:v>공식 단축URL</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="34" customHeight="1">
       <x:c r="A31" s="87" t="n">
@@ -2052,7 +2299,7 @@
         <x:v>신규 버튜버 집계 제외 권장</x:v>
       </x:c>
       <x:c r="J31" s="84" t="str">
-        <x:v>https://x.com/yune_of/status/2079201740860391579</x:v>
+        <x:v>https://chzzk.naver.com/67b160c97b4b04aecfdee08958ca2c34</x:v>
       </x:c>
       <x:c r="K31" s="87" t="str">
         <x:v>확인</x:v>
@@ -2061,6 +2308,12 @@
         <x:f>IF(OR(K31="미공지",K31="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M31" s="134" t="str">
+        <x:v>https://x.com/yune_of/status/2079201740860391579</x:v>
+      </x:c>
+      <x:c r="N31" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="34" customHeight="1">
       <x:c r="A32" s="87" t="n">
@@ -2093,7 +2346,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J32" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/wooch1004/post/167837571</x:v>
+        <x:v>https://www.sooplive.com/station/uchi5757</x:v>
       </x:c>
       <x:c r="K32" s="87" t="str">
         <x:v>확인</x:v>
@@ -2102,6 +2355,12 @@
         <x:f>IF(OR(K32="미공지",K32="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M32" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/uchi5757/post/200016401</x:v>
+      </x:c>
+      <x:c r="N32" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
       <x:c r="A33" s="87" t="n">
@@ -2130,16 +2389,23 @@
         <x:f>IF(B33&lt;$B$3,"완료",IF(B33=$B$3,"당일","예정"))</x:f>
         <x:v>완료</x:v>
       </x:c>
-      <x:c r="I33" s="84" t="str"/>
+      <x:c r="I33" s="84" t="str">
+        <x:v>채널 ID 전체 미확인</x:v>
+      </x:c>
       <x:c r="J33" s="84" t="str">
+        <x:v>미확인</x:v>
+      </x:c>
+      <x:c r="K33" s="87" t="str">
+        <x:v>확인</x:v>
+      </x:c>
+      <x:c r="L33" s="87" t="str">
+        <x:v>검토 필요</x:v>
+      </x:c>
+      <x:c r="M33" s="134" t="str">
         <x:v>https://x.com/Sour__Fox___/status/2078084867397664770</x:v>
       </x:c>
-      <x:c r="K33" s="87" t="str">
-        <x:v>확인</x:v>
-      </x:c>
-      <x:c r="L33" s="87" t="str">
-        <x:f>IF(OR(K33="미공지",K33="재확인 필요"),"검토 필요","등록 가능")</x:f>
-        <x:v>등록 가능</x:v>
+      <x:c r="N33" s="125" t="str">
+        <x:v>미확인</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
@@ -2171,7 +2437,7 @@
         <x:v>원문 ‘5시’ 표기: 오전·오후 재확인 필요</x:v>
       </x:c>
       <x:c r="J34" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/kya030/post/167873256</x:v>
+        <x:v>https://www.sooplive.com/station/keueukya</x:v>
       </x:c>
       <x:c r="K34" s="87" t="str">
         <x:v>재확인 필요</x:v>
@@ -2180,6 +2446,12 @@
         <x:f>IF(OR(K34="미공지",K34="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>검토 필요</x:v>
       </x:c>
+      <x:c r="M34" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/keueukya/post/201655785</x:v>
+      </x:c>
+      <x:c r="N34" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="34" customHeight="1">
       <x:c r="A35" s="87" t="n">
@@ -2212,7 +2484,7 @@
         <x:v>치지직 재데뷔·신규 버튜버 집계 제외 권장</x:v>
       </x:c>
       <x:c r="J35" s="84" t="str">
-        <x:v>https://x.com/aino_sia/status/2081258211425001523/photo/1</x:v>
+        <x:v>https://chzzk.naver.com/4470cfa17a7c9482233898df7135fc14</x:v>
       </x:c>
       <x:c r="K35" s="87" t="str">
         <x:v>확인</x:v>
@@ -2221,6 +2493,12 @@
         <x:f>IF(OR(K35="미공지",K35="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M35" s="134" t="str">
+        <x:v>https://x.com/aino_sia/status/2081258211425001523/photo/1</x:v>
+      </x:c>
+      <x:c r="N35" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="34" customHeight="1">
       <x:c r="A36" s="87" t="n">
@@ -2253,7 +2531,7 @@
         <x:v>데뷔 방송</x:v>
       </x:c>
       <x:c r="J36" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/marung00/post/167918269</x:v>
+        <x:v>https://www.sooplive.com/station/maruruung</x:v>
       </x:c>
       <x:c r="K36" s="87" t="str">
         <x:v>확인</x:v>
@@ -2262,6 +2540,12 @@
         <x:f>IF(OR(K36="미공지",K36="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M36" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/maruruung/post/202018469</x:v>
+      </x:c>
+      <x:c r="N36" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="34" customHeight="1">
       <x:c r="A37" s="87" t="n">
@@ -2284,22 +2568,29 @@
         <x:v>블루니아</x:v>
       </x:c>
       <x:c r="G37" s="87" t="str">
-        <x:v>최초 데뷔</x:v>
+        <x:v>데뷔 유형 재확인</x:v>
       </x:c>
       <x:c r="H37" s="87" t="str">
         <x:f>IF(B37&lt;$B$3,"완료",IF(B37=$B$3,"당일","예정"))</x:f>
         <x:v>당일</x:v>
       </x:c>
-      <x:c r="I37" s="84" t="str"/>
+      <x:c r="I37" s="84" t="str">
+        <x:v>기존 채널 방송 이력 확인됨·최초 데뷔 분류 재검토</x:v>
+      </x:c>
       <x:c r="J37" s="84" t="str">
+        <x:v>https://chzzk.naver.com/94a9dfe3124fb22f4b889e50b1e54382</x:v>
+      </x:c>
+      <x:c r="K37" s="87" t="str">
+        <x:v>확인</x:v>
+      </x:c>
+      <x:c r="L37" s="87" t="str">
+        <x:v>검토 필요</x:v>
+      </x:c>
+      <x:c r="M37" s="134" t="str">
         <x:v>https://www.youtube.com/watch?v=87LBL1u7Ok8</x:v>
       </x:c>
-      <x:c r="K37" s="87" t="str">
-        <x:v>확인</x:v>
-      </x:c>
-      <x:c r="L37" s="87" t="str">
-        <x:f>IF(OR(K37="미공지",K37="재확인 필요"),"검토 필요","등록 가능")</x:f>
-        <x:v>등록 가능</x:v>
+      <x:c r="N37" s="125" t="str">
+        <x:v>확인</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="34" customHeight="1">
@@ -2329,16 +2620,23 @@
         <x:f>IF(B38&lt;$B$3,"완료",IF(B38=$B$3,"당일","예정"))</x:f>
         <x:v>당일</x:v>
       </x:c>
-      <x:c r="I38" s="84" t="str"/>
+      <x:c r="I38" s="84" t="str">
+        <x:v>채널 ID 전체 미확인</x:v>
+      </x:c>
       <x:c r="J38" s="84" t="str">
+        <x:v>미확인</x:v>
+      </x:c>
+      <x:c r="K38" s="87" t="str">
+        <x:v>확인</x:v>
+      </x:c>
+      <x:c r="L38" s="87" t="str">
+        <x:v>검토 필요</x:v>
+      </x:c>
+      <x:c r="M38" s="135" t="str">
         <x:v>https://x.com/Yu_0w0r/status/2079417816948854910</x:v>
       </x:c>
-      <x:c r="K38" s="87" t="str">
-        <x:v>확인</x:v>
-      </x:c>
-      <x:c r="L38" s="87" t="str">
-        <x:f>IF(OR(K38="미공지",K38="재확인 필요"),"검토 필요","등록 가능")</x:f>
-        <x:v>등록 가능</x:v>
+      <x:c r="N38" s="125" t="str">
+        <x:v>미확인</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
@@ -2369,17 +2667,22 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="I39" s="84" t="str">
-        <x:v>예정</x:v>
+        <x:v>예정·채널 ID 전체 미확인</x:v>
       </x:c>
       <x:c r="J39" s="84" t="str">
+        <x:v>미확인</x:v>
+      </x:c>
+      <x:c r="K39" s="87" t="str">
+        <x:v>확인</x:v>
+      </x:c>
+      <x:c r="L39" s="87" t="str">
+        <x:v>검토 필요</x:v>
+      </x:c>
+      <x:c r="M39" s="134" t="str">
         <x:v>https://x.com/Beriaroom/status/2078736030249996427</x:v>
       </x:c>
-      <x:c r="K39" s="87" t="str">
-        <x:v>확인</x:v>
-      </x:c>
-      <x:c r="L39" s="87" t="str">
-        <x:f>IF(OR(K39="미공지",K39="재확인 필요"),"검토 필요","등록 가능")</x:f>
-        <x:v>등록 가능</x:v>
+      <x:c r="N39" s="125" t="str">
+        <x:v>미확인</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="34" customHeight="1">
@@ -2413,7 +2716,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J40" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/ruha0612/post/168012350</x:v>
+        <x:v>https://www.sooplive.com/station/nruha0207</x:v>
       </x:c>
       <x:c r="K40" s="87" t="str">
         <x:v>확인</x:v>
@@ -2422,6 +2725,12 @@
         <x:f>IF(OR(K40="미공지",K40="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M40" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/nruha0207/post/202166111</x:v>
+      </x:c>
+      <x:c r="N40" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="34" customHeight="1">
       <x:c r="A41" s="87" t="n">
@@ -2454,7 +2763,7 @@
         <x:v>재데뷔 예정·신규 버튜버 집계 제외 권장</x:v>
       </x:c>
       <x:c r="J41" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/cheesezz/post/168054144</x:v>
+        <x:v>https://www.sooplive.com/station/ddiddu4</x:v>
       </x:c>
       <x:c r="K41" s="87" t="str">
         <x:v>확인</x:v>
@@ -2463,6 +2772,12 @@
         <x:f>IF(OR(K41="미공지",K41="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M41" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/ddiddu4/post/202245845</x:v>
+      </x:c>
+      <x:c r="N41" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="87" t="n">
@@ -2492,17 +2807,22 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="I42" s="84" t="str">
-        <x:v>Live2D 첫 방송 예정</x:v>
+        <x:v>Live2D 첫 방송 예정·채널 ID 전체 미확인</x:v>
       </x:c>
       <x:c r="J42" s="84" t="str">
+        <x:v>미확인</x:v>
+      </x:c>
+      <x:c r="K42" s="87" t="str">
+        <x:v>확인</x:v>
+      </x:c>
+      <x:c r="L42" s="87" t="str">
+        <x:v>검토 필요</x:v>
+      </x:c>
+      <x:c r="M42" s="135" t="str">
         <x:v>https://x.com/Traumera2/status/2080945881533313116</x:v>
       </x:c>
-      <x:c r="K42" s="87" t="str">
-        <x:v>확인</x:v>
-      </x:c>
-      <x:c r="L42" s="87" t="str">
-        <x:f>IF(OR(K42="미공지",K42="재확인 필요"),"검토 필요","등록 가능")</x:f>
-        <x:v>등록 가능</x:v>
+      <x:c r="N42" s="125" t="str">
+        <x:v>미확인</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="34" customHeight="1">
@@ -2536,7 +2856,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J43" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/tamago611/post/168056587</x:v>
+        <x:v>https://www.sooplive.com/station/krtl6798</x:v>
       </x:c>
       <x:c r="K43" s="87" t="str">
         <x:v>확인</x:v>
@@ -2545,6 +2865,12 @@
         <x:f>IF(OR(K43="미공지",K43="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M43" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/krtl6798/post/202258101</x:v>
+      </x:c>
+      <x:c r="N43" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="34" customHeight="1">
       <x:c r="A44" s="87" t="n">
@@ -2577,7 +2903,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J44" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/ironyang/post/168100669</x:v>
+        <x:v>https://www.sooplive.com/station/ironyan</x:v>
       </x:c>
       <x:c r="K44" s="87" t="str">
         <x:v>확인</x:v>
@@ -2586,6 +2912,12 @@
         <x:f>IF(OR(K44="미공지",K44="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M44" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/ironyan/post/202088647</x:v>
+      </x:c>
+      <x:c r="N44" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="34" customHeight="1">
       <x:c r="A45" s="87" t="n">
@@ -2618,7 +2950,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J45" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/eunha0202/post/168146976</x:v>
+        <x:v>https://www.sooplive.com/station/chaeeunha</x:v>
       </x:c>
       <x:c r="K45" s="87" t="str">
         <x:v>확인</x:v>
@@ -2627,6 +2959,12 @@
         <x:f>IF(OR(K45="미공지",K45="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M45" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/chaeeunha/post/202330115</x:v>
+      </x:c>
+      <x:c r="N45" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="34" customHeight="1">
       <x:c r="A46" s="87" t="n">
@@ -2659,7 +2997,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J46" s="84" t="str">
-        <x:v>https://x.com/noya_yo_o</x:v>
+        <x:v>https://chzzk.naver.com/7513c1b6197bc31b40297991cc043d0f</x:v>
       </x:c>
       <x:c r="K46" s="87" t="str">
         <x:v>확인</x:v>
@@ -2668,6 +3006,12 @@
         <x:f>IF(OR(K46="미공지",K46="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M46" s="135" t="str">
+        <x:v>https://x.com/noya_yo_o</x:v>
+      </x:c>
+      <x:c r="N46" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="34" customHeight="1">
       <x:c r="A47" s="87" t="n">
@@ -2700,7 +3044,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J47" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/ddomo0/post/168150874</x:v>
+        <x:v>https://www.sooplive.com/station/fkvkdpf83</x:v>
       </x:c>
       <x:c r="K47" s="87" t="str">
         <x:v>확인</x:v>
@@ -2709,6 +3053,12 @@
         <x:f>IF(OR(K47="미공지",K47="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M47" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/fkvkdpf83/post/202243339</x:v>
+      </x:c>
+      <x:c r="N47" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="34" customHeight="1">
       <x:c r="A48" s="87" t="n">
@@ -2736,17 +3086,22 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="I48" s="84" t="str">
-        <x:v>예정</x:v>
+        <x:v>예정·채널 ID 전체 미확인</x:v>
       </x:c>
       <x:c r="J48" s="84" t="str">
-        <x:v>https://x.com/SonagiNagi_/status/2080880724324806758</x:v>
+        <x:v>미확인</x:v>
       </x:c>
       <x:c r="K48" s="87" t="str">
         <x:v>미공지</x:v>
       </x:c>
       <x:c r="L48" s="87" t="str">
-        <x:f>IF(OR(K48="미공지",K48="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>검토 필요</x:v>
+      </x:c>
+      <x:c r="M48" s="135" t="str">
+        <x:v>https://x.com/SonagiNagi_/status/2080880724324806758</x:v>
+      </x:c>
+      <x:c r="N48" s="125" t="str">
+        <x:v>미확인</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
@@ -2780,7 +3135,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J49" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/myao0207/post/168459900</x:v>
+        <x:v>https://www.sooplive.com/station/meowuxu</x:v>
       </x:c>
       <x:c r="K49" s="87" t="str">
         <x:v>확인</x:v>
@@ -2789,6 +3144,12 @@
         <x:f>IF(OR(K49="미공지",K49="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M49" s="134" t="str">
+        <x:v>https://www.sooplive.com/station/meowuxu/board/124115167</x:v>
+      </x:c>
+      <x:c r="N49" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="34" customHeight="1">
       <x:c r="A50" s="87" t="n">
@@ -2821,7 +3182,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J50" s="84" t="str">
-        <x:v>https://www.sooplive.co.kr/station/memo/tentash/post/168461822</x:v>
+        <x:v>https://www.sooplive.com/station/xxxsihyeon</x:v>
       </x:c>
       <x:c r="K50" s="87" t="str">
         <x:v>확인</x:v>
@@ -2830,6 +3191,12 @@
         <x:f>IF(OR(K50="미공지",K50="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M50" s="135" t="str">
+        <x:v>https://www.sooplive.com/station/xxxsihyeon/post/202072379</x:v>
+      </x:c>
+      <x:c r="N50" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="34" customHeight="1">
       <x:c r="A51" s="87" t="n">
@@ -2860,7 +3227,7 @@
         <x:v>3D 재데뷔·신규 버튜버 집계 제외 권장</x:v>
       </x:c>
       <x:c r="J51" s="84" t="str">
-        <x:v>https://x.com/Prin030/status/2079282719876637147</x:v>
+        <x:v>https://chzzk.naver.com/ffd9905693aa3cfccd816555c65cdb9a</x:v>
       </x:c>
       <x:c r="K51" s="87" t="str">
         <x:v>미공지</x:v>
@@ -2869,6 +3236,12 @@
         <x:f>IF(OR(K51="미공지",K51="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>검토 필요</x:v>
       </x:c>
+      <x:c r="M51" s="134" t="str">
+        <x:v>https://x.com/Prin030/status/2079282719876637147</x:v>
+      </x:c>
+      <x:c r="N51" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="34" customHeight="1">
       <x:c r="A52" s="87" t="n">
@@ -2901,7 +3274,7 @@
         <x:v>예정</x:v>
       </x:c>
       <x:c r="J52" s="84" t="str">
-        <x:v>https://x.com/myaing1213</x:v>
+        <x:v>https://www.sooplive.com/station/yaaang301</x:v>
       </x:c>
       <x:c r="K52" s="87" t="str">
         <x:v>확인</x:v>
@@ -2910,6 +3283,12 @@
         <x:f>IF(OR(K52="미공지",K52="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
+      <x:c r="M52" s="135" t="str">
+        <x:v>https://x.com/myaing1213</x:v>
+      </x:c>
+      <x:c r="N52" s="125" t="str">
+        <x:v>확인</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="34" customHeight="1">
       <x:c r="A53" s="88" t="n">
@@ -2942,7 +3321,7 @@
         <x:v>V-LUP 데뷔 예정</x:v>
       </x:c>
       <x:c r="J53" s="85" t="str">
-        <x:v>https://x.com/V_LUP_Official</x:v>
+        <x:v>https://chzzk.naver.com/057813a95807a252872ab2b4d84f7f9d</x:v>
       </x:c>
       <x:c r="K53" s="88" t="str">
         <x:v>확인</x:v>
@@ -2950,6 +3329,12 @@
       <x:c r="L53" s="88" t="str">
         <x:f>IF(OR(K53="미공지",K53="재확인 필요"),"검토 필요","등록 가능")</x:f>
         <x:v>등록 가능</x:v>
+      </x:c>
+      <x:c r="M53" s="134" t="str">
+        <x:v>https://x.com/V_LUP_Official</x:v>
+      </x:c>
+      <x:c r="N53" s="125" t="str">
+        <x:v>확인</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -3075,7 +3460,18 @@
   <x:conditionalFormatting sqref="L9:L53">
     <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="검토 필요"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="3">
+  <x:conditionalFormatting sqref="N9:N53">
+    <x:cfRule type="expression" dxfId="5" priority="6">
+      <x:formula>$N9="확인"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="6" priority="7">
+      <x:formula>$N9="공식 단축URL"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="7" priority="8">
+      <x:formula>$N9="미확인"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="E9:E200">
       <x:formula1>"치지직,SOOP"</x:formula1>
     </x:dataValidation>
@@ -3085,11 +3481,14 @@
     <x:dataValidation type="list" sqref="K9:K200">
       <x:formula1>"확인,미공지,재확인 필요"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="N9:N53">
+      <x:formula1>"확인,공식 단축URL,미확인"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8eca6483a0b44f27"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfce6a0e46c6741fd"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb940ccc710d94199"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a4db6362ac5411e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3899,9 +4298,9 @@
       <x:c r="E22" s="122"/>
       <x:c r="F22" s="122"/>
     </x:row>
-    <x:row r="23" ht="32" customHeight="1">
+    <x:row r="23" ht="28" customHeight="1">
       <x:c r="A23" s="122" t="str">
-        <x:v>5. 출처 URL은 삭제·변경 가능성이 있으므로 채널 ID와 게시물 URL을 함께 보관 권장</x:v>
+        <x:v>5. 방송 채널 URL에는 플랫폼 채널 홈 주소만 입력하고, SNS·영상·공지글은 일정 근거 URL에 분리</x:v>
       </x:c>
       <x:c r="B23" s="122"/>
       <x:c r="C23" s="122"/>
@@ -3909,13 +4308,15 @@
       <x:c r="E23" s="122"/>
       <x:c r="F23" s="122"/>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="1"/>
-      <x:c r="B24" s="1"/>
-      <x:c r="C24" s="1"/>
-      <x:c r="D24" s="1"/>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="1"/>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="136" t="str">
+        <x:v>6. 검색 결과에서 채널 ID 전체를 확인할 수 없으면 임의 추정하지 않고 ‘미확인’으로 기록</x:v>
+      </x:c>
+      <x:c r="B24" s="136"/>
+      <x:c r="C24" s="136"/>
+      <x:c r="D24" s="136"/>
+      <x:c r="E24" s="136"/>
+      <x:c r="F24" s="136"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="1"/>
